--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
@@ -320,6 +320,9 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>GEM-ERP-LOG-MedicationDispense.prescriptionId</t>
   </si>
   <si>
@@ -373,9 +376,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel</t>
@@ -2026,21 +2026,21 @@
         <v>76</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2066,10 +2066,10 @@
         <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2120,7 +2120,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>83</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2166,13 +2166,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2223,7 +2223,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>83</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2269,13 +2269,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2326,7 +2326,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>83</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2554,14 +2554,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2574,25 +2574,25 @@
         <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2641,7 +2641,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2650,13 +2650,13 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -2687,7 +2687,7 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>118</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2990,25 +2990,25 @@
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -3057,7 +3057,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3066,13 +3066,13 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -3206,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>127</v>
@@ -3414,7 +3414,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>132</v>
@@ -4037,7 +4037,7 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>143</v>
@@ -4110,7 +4110,7 @@
         <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>80</v>
@@ -4144,7 +4144,7 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>84</v>
@@ -4562,7 +4562,7 @@
         <v>74</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>162</v>
@@ -4669,7 +4669,7 @@
         <v>74</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>84</v>
@@ -4774,10 +4774,10 @@
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>176</v>
@@ -4879,7 +4879,7 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>84</v>
@@ -4986,7 +4986,7 @@
         <v>74</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>124</v>
@@ -5404,7 +5404,7 @@
         <v>74</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>162</v>
@@ -5511,7 +5511,7 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>84</v>
@@ -5616,10 +5616,10 @@
         <v>74</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>199</v>
@@ -5721,7 +5721,7 @@
         <v>74</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>84</v>
@@ -5828,7 +5828,7 @@
         <v>74</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>124</v>
@@ -6246,7 +6246,7 @@
         <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>162</v>
@@ -6353,7 +6353,7 @@
         <v>74</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>84</v>
@@ -6458,10 +6458,10 @@
         <v>74</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>210</v>
@@ -6563,7 +6563,7 @@
         <v>74</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>84</v>
@@ -6670,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>124</v>
@@ -7088,7 +7088,7 @@
         <v>74</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>162</v>
@@ -7195,7 +7195,7 @@
         <v>74</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>84</v>
@@ -7300,10 +7300,10 @@
         <v>74</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>221</v>
@@ -7405,7 +7405,7 @@
         <v>74</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>84</v>
@@ -7512,7 +7512,7 @@
         <v>74</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>124</v>
@@ -7930,7 +7930,7 @@
         <v>74</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>162</v>
@@ -8037,7 +8037,7 @@
         <v>74</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>84</v>
@@ -8142,10 +8142,10 @@
         <v>74</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>232</v>
@@ -8247,7 +8247,7 @@
         <v>74</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>84</v>
@@ -8354,7 +8354,7 @@
         <v>74</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>124</v>
@@ -8875,7 +8875,7 @@
         <v>74</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>143</v>
@@ -8948,7 +8948,7 @@
         <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>80</v>
@@ -8982,7 +8982,7 @@
         <v>74</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>84</v>
@@ -9400,7 +9400,7 @@
         <v>74</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>162</v>
@@ -9507,7 +9507,7 @@
         <v>74</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>84</v>
@@ -9612,10 +9612,10 @@
         <v>74</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>250</v>
@@ -9717,7 +9717,7 @@
         <v>74</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>84</v>
@@ -9824,7 +9824,7 @@
         <v>74</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>124</v>
@@ -10242,7 +10242,7 @@
         <v>74</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>162</v>
@@ -10349,7 +10349,7 @@
         <v>74</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>84</v>
@@ -10454,10 +10454,10 @@
         <v>74</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>232</v>
@@ -10559,7 +10559,7 @@
         <v>74</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>84</v>
@@ -10666,7 +10666,7 @@
         <v>74</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>124</v>
@@ -11084,7 +11084,7 @@
         <v>74</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>162</v>
@@ -11191,7 +11191,7 @@
         <v>74</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>84</v>
@@ -11296,10 +11296,10 @@
         <v>74</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>269</v>
@@ -11401,7 +11401,7 @@
         <v>74</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>84</v>
@@ -11508,7 +11508,7 @@
         <v>74</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>124</v>
@@ -11826,7 +11826,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>278</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12129,25 +12129,25 @@
         <v>74</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>74</v>
@@ -12196,7 +12196,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12205,13 +12205,13 @@
         <v>76</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102">
@@ -12345,7 +12345,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>284</v>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -12650,25 +12650,25 @@
         <v>74</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>74</v>
@@ -12717,7 +12717,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12726,13 +12726,13 @@
         <v>76</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="107">
@@ -13071,7 +13071,7 @@
         <v>74</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>143</v>
@@ -13144,7 +13144,7 @@
         <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>80</v>
@@ -13178,7 +13178,7 @@
         <v>74</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>84</v>
@@ -13596,7 +13596,7 @@
         <v>74</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>162</v>
@@ -13703,7 +13703,7 @@
         <v>74</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>84</v>
@@ -13808,10 +13808,10 @@
         <v>74</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>176</v>
@@ -13913,7 +13913,7 @@
         <v>74</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>84</v>
@@ -14020,7 +14020,7 @@
         <v>74</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>124</v>
@@ -14438,7 +14438,7 @@
         <v>74</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>162</v>
@@ -14545,7 +14545,7 @@
         <v>74</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>84</v>
@@ -14650,10 +14650,10 @@
         <v>74</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>199</v>
@@ -14755,7 +14755,7 @@
         <v>74</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>84</v>
@@ -14862,7 +14862,7 @@
         <v>74</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>124</v>
@@ -15280,7 +15280,7 @@
         <v>74</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>162</v>
@@ -15387,7 +15387,7 @@
         <v>74</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>84</v>
@@ -15492,10 +15492,10 @@
         <v>74</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>210</v>
@@ -15597,7 +15597,7 @@
         <v>74</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>84</v>
@@ -15704,7 +15704,7 @@
         <v>74</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>124</v>
@@ -16122,7 +16122,7 @@
         <v>74</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>162</v>
@@ -16229,7 +16229,7 @@
         <v>74</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>84</v>
@@ -16334,10 +16334,10 @@
         <v>74</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>221</v>
@@ -16439,7 +16439,7 @@
         <v>74</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>84</v>
@@ -16546,7 +16546,7 @@
         <v>74</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>124</v>
@@ -16964,7 +16964,7 @@
         <v>74</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>162</v>
@@ -17071,7 +17071,7 @@
         <v>74</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>84</v>
@@ -17176,10 +17176,10 @@
         <v>74</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>232</v>
@@ -17281,7 +17281,7 @@
         <v>74</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>84</v>
@@ -17388,7 +17388,7 @@
         <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>124</v>
@@ -17910,7 +17910,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>345</v>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -18217,25 +18217,25 @@
         <v>74</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K159" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>74</v>
@@ -18284,7 +18284,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -18293,13 +18293,13 @@
         <v>76</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="160">
@@ -18947,7 +18947,7 @@
         <v>74</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K166" t="s" s="2">
         <v>84</v>
@@ -19024,7 +19024,7 @@
         <v>80</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="167">
@@ -19052,7 +19052,7 @@
         <v>74</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K167" t="s" s="2">
         <v>162</v>
@@ -19129,7 +19129,7 @@
         <v>80</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="168">
@@ -19157,7 +19157,7 @@
         <v>74</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>376</v>
@@ -19228,7 +19228,7 @@
         <v>83</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>80</v>
@@ -19262,7 +19262,7 @@
         <v>74</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>84</v>
@@ -19339,7 +19339,7 @@
         <v>80</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="170">
@@ -19992,7 +19992,7 @@
         <v>74</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L176" t="s" s="2">
         <v>400</v>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -20297,25 +20297,25 @@
         <v>74</v>
       </c>
       <c r="I179" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K179" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>74</v>
@@ -20364,7 +20364,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -20373,13 +20373,13 @@
         <v>76</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="180">

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
@@ -320,9 +320,6 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>GEM-ERP-LOG-MedicationDispense.prescriptionId</t>
   </si>
   <si>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel</t>
@@ -2026,21 +2026,21 @@
         <v>76</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2066,10 +2066,10 @@
         <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2120,7 +2120,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>83</v>
@@ -2140,10 +2140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2166,13 +2166,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2223,7 +2223,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>83</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2269,13 +2269,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>107</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2326,7 +2326,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>83</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2449,10 +2449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2554,14 +2554,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2574,25 +2574,25 @@
         <v>74</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -2641,7 +2641,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2650,13 +2650,13 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -2687,7 +2687,7 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>118</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2990,25 +2990,25 @@
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -3057,7 +3057,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3066,13 +3066,13 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -3206,7 +3206,7 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>127</v>
@@ -3414,7 +3414,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>132</v>
@@ -4037,7 +4037,7 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>143</v>
@@ -4110,7 +4110,7 @@
         <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>80</v>
@@ -4144,7 +4144,7 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>84</v>
@@ -4562,7 +4562,7 @@
         <v>74</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>162</v>
@@ -4669,7 +4669,7 @@
         <v>74</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>84</v>
@@ -4774,10 +4774,10 @@
         <v>74</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>176</v>
@@ -4879,7 +4879,7 @@
         <v>74</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>84</v>
@@ -4986,7 +4986,7 @@
         <v>74</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>124</v>
@@ -5404,7 +5404,7 @@
         <v>74</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>162</v>
@@ -5511,7 +5511,7 @@
         <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>84</v>
@@ -5616,10 +5616,10 @@
         <v>74</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>199</v>
@@ -5721,7 +5721,7 @@
         <v>74</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>84</v>
@@ -5828,7 +5828,7 @@
         <v>74</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>124</v>
@@ -6246,7 +6246,7 @@
         <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>162</v>
@@ -6353,7 +6353,7 @@
         <v>74</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>84</v>
@@ -6458,10 +6458,10 @@
         <v>74</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>210</v>
@@ -6563,7 +6563,7 @@
         <v>74</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>84</v>
@@ -6670,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>124</v>
@@ -7088,7 +7088,7 @@
         <v>74</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>162</v>
@@ -7195,7 +7195,7 @@
         <v>74</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>84</v>
@@ -7300,10 +7300,10 @@
         <v>74</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>221</v>
@@ -7405,7 +7405,7 @@
         <v>74</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>84</v>
@@ -7512,7 +7512,7 @@
         <v>74</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>124</v>
@@ -7930,7 +7930,7 @@
         <v>74</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>162</v>
@@ -8037,7 +8037,7 @@
         <v>74</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>84</v>
@@ -8142,10 +8142,10 @@
         <v>74</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>232</v>
@@ -8247,7 +8247,7 @@
         <v>74</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>84</v>
@@ -8354,7 +8354,7 @@
         <v>74</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>124</v>
@@ -8875,7 +8875,7 @@
         <v>74</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>143</v>
@@ -8948,7 +8948,7 @@
         <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>80</v>
@@ -8982,7 +8982,7 @@
         <v>74</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>84</v>
@@ -9400,7 +9400,7 @@
         <v>74</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>162</v>
@@ -9507,7 +9507,7 @@
         <v>74</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>84</v>
@@ -9612,10 +9612,10 @@
         <v>74</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>250</v>
@@ -9717,7 +9717,7 @@
         <v>74</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>84</v>
@@ -9824,7 +9824,7 @@
         <v>74</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>124</v>
@@ -10242,7 +10242,7 @@
         <v>74</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>162</v>
@@ -10349,7 +10349,7 @@
         <v>74</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>84</v>
@@ -10454,10 +10454,10 @@
         <v>74</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>232</v>
@@ -10559,7 +10559,7 @@
         <v>74</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>84</v>
@@ -10666,7 +10666,7 @@
         <v>74</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>124</v>
@@ -11084,7 +11084,7 @@
         <v>74</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>162</v>
@@ -11191,7 +11191,7 @@
         <v>74</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>84</v>
@@ -11296,10 +11296,10 @@
         <v>74</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>269</v>
@@ -11401,7 +11401,7 @@
         <v>74</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>84</v>
@@ -11508,7 +11508,7 @@
         <v>74</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>124</v>
@@ -11826,7 +11826,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>278</v>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12129,25 +12129,25 @@
         <v>74</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>74</v>
@@ -12196,7 +12196,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12205,13 +12205,13 @@
         <v>76</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102">
@@ -12345,7 +12345,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>284</v>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -12650,25 +12650,25 @@
         <v>74</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>74</v>
@@ -12717,7 +12717,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12726,13 +12726,13 @@
         <v>76</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107">
@@ -13071,7 +13071,7 @@
         <v>74</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>143</v>
@@ -13144,7 +13144,7 @@
         <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>80</v>
@@ -13178,7 +13178,7 @@
         <v>74</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>84</v>
@@ -13596,7 +13596,7 @@
         <v>74</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>162</v>
@@ -13703,7 +13703,7 @@
         <v>74</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>84</v>
@@ -13808,10 +13808,10 @@
         <v>74</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>176</v>
@@ -13913,7 +13913,7 @@
         <v>74</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>84</v>
@@ -14020,7 +14020,7 @@
         <v>74</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>124</v>
@@ -14438,7 +14438,7 @@
         <v>74</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>162</v>
@@ -14545,7 +14545,7 @@
         <v>74</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>84</v>
@@ -14650,10 +14650,10 @@
         <v>74</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>199</v>
@@ -14755,7 +14755,7 @@
         <v>74</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>84</v>
@@ -14862,7 +14862,7 @@
         <v>74</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>124</v>
@@ -15280,7 +15280,7 @@
         <v>74</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>162</v>
@@ -15387,7 +15387,7 @@
         <v>74</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>84</v>
@@ -15492,10 +15492,10 @@
         <v>74</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>210</v>
@@ -15597,7 +15597,7 @@
         <v>74</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>84</v>
@@ -15704,7 +15704,7 @@
         <v>74</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>124</v>
@@ -16122,7 +16122,7 @@
         <v>74</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>162</v>
@@ -16229,7 +16229,7 @@
         <v>74</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>84</v>
@@ -16334,10 +16334,10 @@
         <v>74</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>221</v>
@@ -16439,7 +16439,7 @@
         <v>74</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>84</v>
@@ -16546,7 +16546,7 @@
         <v>74</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>124</v>
@@ -16964,7 +16964,7 @@
         <v>74</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>162</v>
@@ -17071,7 +17071,7 @@
         <v>74</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>84</v>
@@ -17176,10 +17176,10 @@
         <v>74</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>232</v>
@@ -17281,7 +17281,7 @@
         <v>74</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>84</v>
@@ -17388,7 +17388,7 @@
         <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>124</v>
@@ -17910,7 +17910,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>345</v>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -18217,25 +18217,25 @@
         <v>74</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K159" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>74</v>
@@ -18284,7 +18284,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -18293,13 +18293,13 @@
         <v>76</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160">
@@ -18947,7 +18947,7 @@
         <v>74</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K166" t="s" s="2">
         <v>84</v>
@@ -19024,7 +19024,7 @@
         <v>80</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167">
@@ -19052,7 +19052,7 @@
         <v>74</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K167" t="s" s="2">
         <v>162</v>
@@ -19129,7 +19129,7 @@
         <v>80</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168">
@@ -19157,7 +19157,7 @@
         <v>74</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>376</v>
@@ -19228,7 +19228,7 @@
         <v>83</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>80</v>
@@ -19262,7 +19262,7 @@
         <v>74</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K169" t="s" s="2">
         <v>84</v>
@@ -19339,7 +19339,7 @@
         <v>80</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170">
@@ -19992,7 +19992,7 @@
         <v>74</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L176" t="s" s="2">
         <v>400</v>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
@@ -20297,25 +20297,25 @@
         <v>74</v>
       </c>
       <c r="I179" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K179" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L179" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M179" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="N179" t="s" s="2">
         <v>93</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>74</v>
@@ -20364,7 +20364,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -20373,13 +20373,13 @@
         <v>76</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="180">

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
@@ -393,9 +393,6 @@
     <t>Erweiterungen</t>
   </si>
   <si>
-    <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.modifierExtension</t>
-  </si>
-  <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.extension.impfung</t>
   </si>
   <si>
@@ -439,6 +436,9 @@
     <t>Angabe zur Verpackung</t>
   </si>
   <si>
+    <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.modifierExtension</t>
+  </si>
+  <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.code</t>
   </si>
   <si>
@@ -875,10 +875,10 @@
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.inhaltsstoffe.extension</t>
   </si>
   <si>
+    <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.inhaltsstoffe.extension.darreichungsform</t>
+  </si>
+  <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.inhaltsstoffe.modifierExtension</t>
-  </si>
-  <si>
-    <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.inhaltsstoffe.extension.darreichungsform</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel.inhaltsstoffe.inhaltsstoff</t>
@@ -2977,39 +2977,35 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
@@ -3057,30 +3053,30 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3103,13 +3099,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3160,7 +3156,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>83</v>
@@ -3180,10 +3176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3191,7 +3187,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>83</v>
@@ -3206,15 +3202,17 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>74</v>
@@ -3263,10 +3261,10 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>83</v>
@@ -3283,10 +3281,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3309,16 +3307,16 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3368,7 +3366,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3388,10 +3386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3414,16 +3412,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3473,7 +3471,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3493,10 +3491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3522,13 +3520,13 @@
         <v>84</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3578,7 +3576,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3598,44 +3596,46 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>74</v>
       </c>
@@ -3683,22 +3683,22 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21">
@@ -4891,7 +4891,7 @@
         <v>181</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>182</v>
@@ -4989,7 +4989,7 @@
         <v>111</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>186</v>
@@ -5733,7 +5733,7 @@
         <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>182</v>
@@ -5831,7 +5831,7 @@
         <v>111</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>186</v>
@@ -6575,7 +6575,7 @@
         <v>212</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>182</v>
@@ -6673,7 +6673,7 @@
         <v>111</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>186</v>
@@ -7417,7 +7417,7 @@
         <v>223</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>182</v>
@@ -7515,7 +7515,7 @@
         <v>111</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>186</v>
@@ -8259,7 +8259,7 @@
         <v>234</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>182</v>
@@ -8357,7 +8357,7 @@
         <v>111</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>186</v>
@@ -9729,7 +9729,7 @@
         <v>252</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O78" t="s" s="2">
         <v>182</v>
@@ -9827,7 +9827,7 @@
         <v>111</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>186</v>
@@ -10571,7 +10571,7 @@
         <v>234</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>182</v>
@@ -10669,7 +10669,7 @@
         <v>111</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>186</v>
@@ -11413,7 +11413,7 @@
         <v>271</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>182</v>
@@ -11511,7 +11511,7 @@
         <v>111</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>186</v>
@@ -11730,7 +11730,7 @@
         <v>276</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12116,39 +12116,35 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>74</v>
       </c>
@@ -12196,22 +12192,22 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>115</v>
+        <v>281</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102">
@@ -12223,35 +12219,39 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>238</v>
+        <v>112</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>74</v>
       </c>
@@ -12299,22 +12299,22 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>282</v>
+        <v>115</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103">
@@ -13925,7 +13925,7 @@
         <v>181</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>182</v>
@@ -14023,7 +14023,7 @@
         <v>111</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>186</v>
@@ -14767,7 +14767,7 @@
         <v>201</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>182</v>
@@ -14865,7 +14865,7 @@
         <v>111</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>186</v>
@@ -15609,7 +15609,7 @@
         <v>212</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>182</v>
@@ -15707,7 +15707,7 @@
         <v>111</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>186</v>
@@ -16451,7 +16451,7 @@
         <v>223</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>182</v>
@@ -16549,7 +16549,7 @@
         <v>111</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L143" t="s" s="2">
         <v>186</v>
@@ -17293,7 +17293,7 @@
         <v>234</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O150" t="s" s="2">
         <v>182</v>
@@ -17391,7 +17391,7 @@
         <v>111</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>186</v>
@@ -19585,7 +19585,7 @@
         <v>392</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -19793,7 +19793,7 @@
         <v>396</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -20410,7 +20410,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L180" t="s" s="2">
         <v>405</v>
